--- a/viewer/downloads/CCA_Alignment.xlsx
+++ b/viewer/downloads/CCA_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +124,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -492,9 +498,9 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,15 +580,19 @@
           <t>9.3.6.7, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>9.3.6.7 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.6.7 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -618,15 +628,19 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -649,15 +663,19 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -688,10 +706,10 @@
           <t>Zero and negative exponents</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -712,15 +730,19 @@
           <t>9.3.5.8, 9.3.6.1, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.3, 7.SP.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.3 (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -756,15 +778,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -787,15 +813,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -831,15 +861,19 @@
           <t>9.3.7.1, 9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -862,15 +896,19 @@
           <t>9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -893,15 +931,19 @@
           <t>9.3.5.5, 9.3.7.1, 9.3.7.4, 9.3.7.5, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.A.8, 8.EE.B.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -937,15 +979,19 @@
           <t>9.1.1.11, 9.1.1.6, 9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.11 (MN-2022), 9.1.1.6 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 6.RP.A.3.C, 7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 6.RP.A.3.C (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.1.1.11 (MN-2022), 9.1.1.6 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -968,15 +1014,19 @@
           <t>9.1.1.11, 9.1.1.15, 9.1.1.5, 9.1.1.6, 9.1.1.8, 9.2.3.6, 9.3.5.6</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.11 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.5 (MN-2022), 9.1.1.6 (MN-2022), 9.1.1.8 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 6.EE.A.2.A, 6.EE.A.3, 6.NS.C.6.B, 6.RP.A.3.C, 7.Sp.8a</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 6.EE.A.2.A (CCSS-M), 6.EE.A.3 (CCSS-M), 6.NS.C.6.B (CCSS-M), 6.RP.A.3.C (CCSS-M), 7.Sp.8a (CCSS-M), 9.1.1.11 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.5 (MN-2022), 9.1.1.6 (MN-2022), 9.1.1.8 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1012,15 +1062,19 @@
           <t>9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.A.8, 8.EE.B.7, 8.G.2</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1043,15 +1097,19 @@
           <t>9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1074,15 +1132,19 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.2, 9.3.7.6, 9.3.7.7, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.EE.C.7.A, 8.G.B.1</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.G.B.1 (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1105,15 +1167,19 @@
           <t>9.3.5.2, 9.3.5.6, 9.3.6.8, 9.3.7.1, 9.3.7.2</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.2 (MN-2022), 9.3.5.6 (MN-2022), 9.3.6.8 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.Sp.8a, 8.EE.C.7.A, MP8</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.2 (MN-2022), 9.3.5.6 (MN-2022), 9.3.6.8 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), MP8 (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1149,15 +1215,19 @@
           <t>9.2.3.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1180,15 +1250,19 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.4</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.4 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.4b, 7.SP.8a</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.4b (CCSS-M), 7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.4 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1211,15 +1285,19 @@
           <t>9.2.3.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.EE.4a, 7.EE.A.1.A, 7.SP.8a, 8.EE.A.8, 8.EE.C.7.A, see ebook</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1 (CCSS-M), 7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1255,15 +1333,19 @@
           <t>9.3.6.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.4a, see ebook</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.4a (CCSS-M), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1286,15 +1368,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1312,10 +1398,10 @@
           <t>Graphing Two-Variable Inequalities</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1336,15 +1422,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1380,15 +1470,19 @@
           <t>9.1.2.5</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>9.1.2.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>6.NS.3</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>6.NS.3 (CCSS-M), 9.1.2.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1411,15 +1505,19 @@
           <t>9.3.5.3, 9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.3 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>7.SP.8a, 7.SP.8b</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M), 9.3.5.3 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1437,10 +1535,10 @@
           <t>Intersection of Two Functions</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1461,15 +1559,19 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>7.SP.8a</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1505,15 +1607,19 @@
           <t>9.3.7.2, 9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.G.C.1</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.G.C.1 (CCSS-M), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1536,15 +1642,19 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A (CCSS-M), 6.NS.C.7.A (CCSS-M), 6.NS.C.7.B (CCSS-M), 6.NS.C.7.D (CCSS-M), 9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1567,15 +1677,19 @@
           <t>9.2.3.7, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.7 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.2.3.7 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CCA_Alignment.xlsx
+++ b/viewer/downloads/CCA_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,7 +119,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -498,7 +492,7 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
@@ -580,17 +574,13 @@
           <t>9.3.6.7, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.6.7 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.6.7 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -628,17 +618,13 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -663,17 +649,13 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.6 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.1.3 (MN-2007), 9.3.7.1 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -706,10 +688,10 @@
           <t>Zero and negative exponents</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -730,17 +712,13 @@
           <t>9.3.5.8, 9.3.6.1, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.3, 7.SP.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.3 (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.2 (MN-2007), 9.2.3.7 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -778,17 +756,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -813,17 +787,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -861,17 +831,13 @@
           <t>9.3.7.1, 9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.4 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -896,17 +862,13 @@
           <t>9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.4 (MN-2007), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -931,17 +893,13 @@
           <t>9.3.5.5, 9.3.7.1, 9.3.7.4, 9.3.7.5, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.A.8, 8.EE.B.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.4 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.5.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -979,17 +937,13 @@
           <t>9.1.1.11, 9.1.1.6, 9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 6.RP.A.3.C, 7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 6.RP.A.3.C (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.1.1.11 (MN-2022), 9.1.1.6 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.11 (MN-2022), 9.1.1.6 (MN-2022), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.6 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.2.4.8 (MN-2007), 9.3.1.3 (MN-2007), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022), 9.4.1.3 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1014,17 +968,13 @@
           <t>9.1.1.11, 9.1.1.15, 9.1.1.5, 9.1.1.6, 9.1.1.8, 9.2.3.6, 9.3.5.6</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 6.EE.A.2.A, 6.EE.A.3, 6.NS.C.6.B, 6.RP.A.3.C, 7.Sp.8a</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 6.EE.A.2.A (CCSS-M), 6.EE.A.3 (CCSS-M), 6.NS.C.6.B (CCSS-M), 6.RP.A.3.C (CCSS-M), 7.Sp.8a (CCSS-M), 9.1.1.11 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.5 (MN-2022), 9.1.1.6 (MN-2022), 9.1.1.8 (MN-2022), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.11 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.5 (MN-2022), 9.1.1.6 (MN-2022), 9.1.1.8 (MN-2022), 9.2.3.6 (MN-2022), 9.2.4.8 (MN-2007), 9.3.1.3 (MN-2007), 9.3.5.6 (MN-2022), 9.4.1.3 (MN-2007), 9.4.2.2 (MN-2007), 9.4.3.4 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1062,17 +1012,13 @@
           <t>9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.A.8, 8.EE.B.7, 8.G.2</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.1 (MN-2007), 9.2.1.3 (MN-2007), 9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.1.9 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1097,17 +1043,13 @@
           <t>9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.6 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.2.4.8 (MN-2007), 9.3.1.3 (MN-2007), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1132,17 +1074,13 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.2, 9.3.7.6, 9.3.7.7, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.EE.C.7.A, 8.G.B.1</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.G.B.1 (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.3 (MN-2007), 9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.5 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.3.6 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.1.3 (MN-2007), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1167,17 +1105,13 @@
           <t>9.3.5.2, 9.3.5.6, 9.3.6.8, 9.3.7.1, 9.3.7.2</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.Sp.8a, 8.EE.C.7.A, MP8</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.2 (MN-2022), 9.3.5.6 (MN-2022), 9.3.6.8 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), MP8 (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.3.6 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.2.4.8 (MN-2007), 9.3.5.2 (MN-2022), 9.3.5.6 (MN-2022), 9.3.6.8 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1215,17 +1149,13 @@
           <t>9.2.3.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.6 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.1.3 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1250,17 +1180,13 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.4</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.4b, 7.SP.8a</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.4b (CCSS-M), 7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.4 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>9.2.3.3 (MN-2007), 9.2.3.7 (MN-2007), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.4 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1285,17 +1211,13 @@
           <t>9.2.3.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.EE.4a, 7.EE.A.1.A, 7.SP.8a, 8.EE.A.8, 8.EE.C.7.A, see ebook</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1 (CCSS-M), 7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.5 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.3.6 (MN-2022), 9.2.3.7 (MN-2007), 9.2.4.1 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.1.3 (MN-2007), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1333,17 +1255,13 @@
           <t>9.3.6.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.4a, see ebook</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.4a (CCSS-M), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.5 (MN-2007), 9.2.4.1 (MN-2007), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1368,17 +1286,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1398,10 +1312,10 @@
           <t>Graphing Two-Variable Inequalities</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
+      <c r="D34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1422,17 +1336,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1470,17 +1380,13 @@
           <t>9.1.2.5</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>6.NS.3</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>6.NS.3 (CCSS-M), 9.1.2.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>9.1.2.5 (MN-2022), 9.4.3.9 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1505,17 +1411,13 @@
           <t>9.3.5.3, 9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>7.SP.8a, 7.SP.8b</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M), 9.3.5.3 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>9.2.3.5 (MN-2007), 9.2.3.7 (MN-2007), 9.2.4.3 (MN-2007), 9.3.5.3 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1535,10 +1437,10 @@
           <t>Intersection of Two Functions</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="9" t="inlineStr"/>
-      <c r="G39" s="9" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1559,17 +1461,13 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>7.SP.8a</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>9.2.3.7 (MN-2007), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1607,17 +1505,13 @@
           <t>9.3.7.2, 9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.G.C.1</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.G.C.1 (CCSS-M), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.2 (MN-2007), 9.2.1.7 (MN-2007), 9.2.1.9 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1642,17 +1536,13 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A (CCSS-M), 6.NS.C.7.A (CCSS-M), 6.NS.C.7.B (CCSS-M), 6.NS.C.7.D (CCSS-M), 9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022), 9.4.1.1 (MN-2007), 9.4.1.4 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1677,17 +1567,13 @@
           <t>9.2.3.7, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.2.3.7 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.7 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
